--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$18</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +77,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,11 +95,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15108,7 +15126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15157,6 +15175,235 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0019 'BK Mladá Boleslav' ROZBITÝ prev CLUB_S2012_13_0017 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0020 'HC Olomouc' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0016 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0024 'HC Olomouc' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0016 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0070 'VSK Technika Brno' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0032 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0079 'David Servis České Budějovice (JČ)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0105 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0079 'David Servis České Budějovice (JČ)' prev→CLUB_S2012_13_0105 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0082 'HC Uničov (JM)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0258 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0083 'SK Karviná (MS)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0261 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0256 'Spartak Velká Bíteš B' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0241 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0256 'Spartak Velká Bíteš B' prev→CLUB_S2012_13_0241 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0267 'HC Brumov – Bylnice (ZLI)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0239 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2013_14_0267 'HC Brumov – Bylnice (ZLI)' prev→CLUB_S2012_13_0239 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0010</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2013_14_0010 'Baráž' (L15, parent=NODE_S2013_14_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0018</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2013_14_0018 'Baráž o I.ligu' (L15, parent=NODE_S2013_14_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0030</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2013_14_0030 'Baráž o 2.ligu' (L25, parent=NODE_S2013_14_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0032</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2013_14_0032 'Kvalifikace o postup do II.ligy' (L25, parent=NODE_S2013_14_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0146</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2013_14_0146 'Baráž o KLM' (L45, parent=NODE_S2013_14_0131) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -43863,6 +44110,435 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0019</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0019 'BK Mladá Boleslav' ROZBITÝ prev CLUB_S2012_13_0017 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0020</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0020 'HC Olomouc' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0016 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0024</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0024 'HC Olomouc' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0016 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0070</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0070 'VSK Technika Brno' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0032 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0079</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0079 'David Servis České Budějovice (JČ)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0105 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0079</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0079 'David Servis České Budějovice (JČ)' prev→CLUB_S2012_13_0105 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0082</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0082 'HC Uničov (JM)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0258 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0083</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0083 'SK Karviná (MS)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0261 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0256</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0256 'Spartak Velká Bíteš B' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0241 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0256</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0256 'Spartak Velká Bíteš B' prev→CLUB_S2012_13_0241 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0267</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0267 'HC Brumov – Bylnice (ZLI)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0239 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0267</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0267 'HC Brumov – Bylnice (ZLI)' prev→CLUB_S2012_13_0239 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0010</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2013_14_0010 'Baráž' (L15, parent=NODE_S2013_14_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0018</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2013_14_0018 'Baráž o I.ligu' (L15, parent=NODE_S2013_14_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0030</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2013_14_0030 'Baráž o 2.ligu' (L25, parent=NODE_S2013_14_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0032</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2013_14_0032 'Kvalifikace o postup do II.ligy' (L25, parent=NODE_S2013_14_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0146</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2013_14_0146 'Baráž o KLM' (L45, parent=NODE_S2013_14_0131) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0017</t>
+          <t>CLUB_S2012_13_0015</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15175,235 +15175,6 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0019 'BK Mladá Boleslav' ROZBITÝ prev CLUB_S2012_13_0017 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0020 'HC Olomouc' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0016 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0024 'HC Olomouc' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0016 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0070 'VSK Technika Brno' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0032 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0079 'David Servis České Budějovice (JČ)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0105 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0079 'David Servis České Budějovice (JČ)' prev→CLUB_S2012_13_0105 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0082 'HC Uničov (JM)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0258 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0083 'SK Karviná (MS)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0261 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0256 'Spartak Velká Bíteš B' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0241 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0256 'Spartak Velká Bíteš B' prev→CLUB_S2012_13_0241 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0267 'HC Brumov – Bylnice (ZLI)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0239 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id: CLUB_S2013_14_0267 'HC Brumov – Bylnice (ZLI)' prev→CLUB_S2012_13_0239 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0010</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2013_14_0010 'Baráž' (L15, parent=NODE_S2013_14_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0018</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2013_14_0018 'Baráž o I.ligu' (L15, parent=NODE_S2013_14_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0030</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2013_14_0030 'Baráž o 2.ligu' (L25, parent=NODE_S2013_14_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0032</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2013_14_0032 'Kvalifikace o postup do II.ligy' (L25, parent=NODE_S2013_14_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0146</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2013_14_0146 'Baráž o KLM' (L45, parent=NODE_S2013_14_0131) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -30634,7 +30405,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -30785,7 +30556,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -31208,7 +30979,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -31396,7 +31167,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -31428,7 +31199,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0017</t>
+          <t>CLUB_S2012_13_0015</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -31537,7 +31308,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -31631,7 +31402,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -32153,7 +31924,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sportovní klub Kadaň</t>
+          <t>Kadaň</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -32388,7 +32159,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sportovní klub Kadaň</t>
+          <t>Kadaň</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -32712,7 +32483,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>SC Kolín</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -32900,7 +32671,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>SC Kolín</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -33093,7 +32864,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -33187,7 +32958,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -33234,7 +33005,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -33328,7 +33099,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -33422,7 +33193,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -33469,7 +33240,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SHC Maso Brejcha Klatovy</t>
+          <t>Klatovy</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -33657,7 +33428,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>RT Torax Poruba</t>
+          <t>Poruba</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -33845,7 +33616,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -35725,7 +35496,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -35918,7 +35689,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>UHK LEV Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -36680,7 +36451,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -36727,7 +36498,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -38986,7 +38757,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>SKP Rapid Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -39085,7 +38856,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -39951,7 +39722,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>IHT Brimstones Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -39998,7 +39769,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>PSK 96 Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -40703,7 +40474,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>BK JTC Nová Paka</t>
+          <t>Nová Paka</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -40844,7 +40615,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -41037,7 +40808,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -41856,7 +41627,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Závodní hokejové Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -41898,7 +41669,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Kohouti Česká Třebová</t>
+          <t>Česká Třebová</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -42848,7 +42619,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>HLC Bulldogs Brno</t>
+          <t>Bulldogs Brno</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -43318,7 +43089,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>HCM Warrior Brno</t>
+          <t>Brno</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -43835,7 +43606,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -43882,7 +43653,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -43929,7 +43700,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>RT Torax Poruba</t>
+          <t>Poruba</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -44116,11 +43887,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -44160,381 +43931,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0019</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0019 'BK Mladá Boleslav' ROZBITÝ prev CLUB_S2012_13_0017 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0020</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0020 'HC Olomouc' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0016 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0024</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0024 'HC Olomouc' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0016 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0070</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0070 'VSK Technika Brno' TBD: auto-prev_club_id oprava → CLUB_S2012_13_0032 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0079</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0079 'David Servis České Budějovice (JČ)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0105 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0079</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0079 'David Servis České Budějovice (JČ)' prev→CLUB_S2012_13_0105 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0082</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0082 'HC Uničov (JM)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0258 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0083</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0083 'SK Karviná (MS)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0261 (strong, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0256</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0256 'Spartak Velká Bíteš B' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0241 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0256</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0256 'Spartak Velká Bíteš B' prev→CLUB_S2012_13_0241 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0267</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0267 'HC Brumov – Bylnice (ZLI)' TBD: auto-prev_club_id doplnění → CLUB_S2012_13_0239 (weak, jméno+město; verifikovat) [fix_continuity] (sezóna bez change_note sloupce)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0267</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>CLUB_S2013_14_0267 'HC Brumov – Bylnice (ZLI)' prev→CLUB_S2012_13_0239 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>pyramida</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0010</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>SYSTEM NODE_S2013_14_0010 'Baráž' (L15, parent=NODE_S2013_14_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>pyramida</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0018</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>SYSTEM NODE_S2013_14_0018 'Baráž o I.ligu' (L15, parent=NODE_S2013_14_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>pyramida</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0030</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>SYSTEM NODE_S2013_14_0030 'Baráž o 2.ligu' (L25, parent=NODE_S2013_14_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>pyramida</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0032</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>SYSTEM NODE_S2013_14_0032 'Kvalifikace o postup do II.ligy' (L25, parent=NODE_S2013_14_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>pyramida</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0146</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>SYSTEM NODE_S2013_14_0146 'Baráž o KLM' (L45, parent=NODE_S2013_14_0131) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(žádné otevřené položky — sezóna OK)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F18"/>
+  <autoFilter ref="A1:F2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -12101,6 +12101,11 @@
           <t>CLUB_S2012_13_0239</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>setrval?</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>TR_S2013_14_00267</t>
@@ -15247,7 +15252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K249"/>
+  <dimension ref="A1:L249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15306,6 +15311,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15343,6 +15353,11 @@
           <t>14 týmů (4-col): základ + předkolo/QF/SF/finále + Play Out + baráž. Mistr: PSG Zlín.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15380,6 +15395,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0004</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15417,6 +15437,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0007</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15491,6 +15516,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0010</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15528,6 +15558,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0011</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15565,6 +15600,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0014</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15602,6 +15642,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0015</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15750,6 +15795,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0022</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15787,6 +15837,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0023</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15824,6 +15879,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0024</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15861,6 +15921,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15898,6 +15963,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16009,6 +16079,11 @@
           <t>II.liga: skupiny + QF/SF/finále + baráž o 2.ligu.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0039</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16083,6 +16158,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0041</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16120,6 +16200,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0048</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16157,6 +16242,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0049</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16194,6 +16284,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0050</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16231,6 +16326,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0042</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16268,6 +16368,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0043</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16305,6 +16410,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0044</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16342,6 +16452,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0047</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16379,6 +16494,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0046</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16707,6 +16827,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0033</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16887,6 +17012,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0051</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -17474,6 +17604,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0056</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17950,6 +18085,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0059</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -19721,6 +19861,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0074</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -19827,6 +19972,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0075</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -20118,6 +20268,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0078</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -20816,6 +20971,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0082</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -21995,6 +22155,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0092</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -22878,6 +23043,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0093</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -23574,6 +23744,11 @@
       <c r="J226" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0098</t>
         </is>
       </c>
     </row>

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -15252,7 +15252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L249"/>
+  <dimension ref="A1:N249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15316,6 +15316,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15474,10 +15484,28 @@
           <t>NODE_S2013_14_0003</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0005</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0009</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>7.–10. ZČ</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -15511,6 +15539,12 @@
           <t>NODE_S2013_14_0003</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15520,6 +15554,14 @@
         <is>
           <t>NODE_S2012_13_0010</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1.–6. ZČ + 2 z předkola</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -15553,6 +15595,12 @@
           <t>NODE_S2013_14_0003</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15562,6 +15610,14 @@
         <is>
           <t>NODE_S2012_13_0011</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -15637,6 +15693,8 @@
           <t>NODE_S2013_14_0003</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15646,6 +15704,14 @@
         <is>
           <t>NODE_S2012_13_0015</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -15679,10 +15745,20 @@
           <t>NODE_S2013_14_0001</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>11.–14. ZČ + poražení předkola</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -16561,11 +16637,6 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>REG_CS</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>NODE_S2013_14_0019</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -15400,6 +15400,16 @@
           <t>NODE_S2013_14_0001</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0004</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0009</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15409,6 +15419,14 @@
         <is>
           <t>NODE_S2012_13_0004</t>
         </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -15501,11 +15519,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>7.–10. ZČ</t>
+          <t>střed tabulky ZČ</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -15557,11 +15575,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.–6. ZČ + 2 z předkola</t>
+          <t>horní ZČ + postupující z předkola</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -15600,7 +15618,11 @@
           <t>NODE_S2013_14_0008</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0007</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15617,7 +15639,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -15651,6 +15673,8 @@
           <t>NODE_S2013_14_0003</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15660,6 +15684,14 @@
         <is>
           <t>NODE_S2012_13_0014</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -15711,7 +15743,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -15754,11 +15786,11 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>11.–14. ZČ + poražení předkola</t>
+          <t>dolní část ZČ</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -15866,6 +15898,16 @@
           <t>NODE_S2013_14_0011</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0013</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0017</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15875,6 +15917,14 @@
         <is>
           <t>NODE_S2012_13_0022</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -15908,6 +15958,16 @@
           <t>NODE_S2013_14_0011</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0014</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0017</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15917,6 +15977,14 @@
         <is>
           <t>NODE_S2012_13_0023</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -15950,6 +16018,12 @@
           <t>NODE_S2013_14_0011</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0015</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15959,6 +16033,14 @@
         <is>
           <t>NODE_S2012_13_0024</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -15992,6 +16074,12 @@
           <t>NODE_S2013_14_0011</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0016</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16001,6 +16089,14 @@
         <is>
           <t>NODE_S2012_13_0025</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -16034,6 +16130,8 @@
           <t>NODE_S2013_14_0011</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16043,6 +16141,14 @@
         <is>
           <t>NODE_S2012_13_0026</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -16076,10 +16182,20 @@
           <t>NODE_S2013_14_0011</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -16355,6 +16471,12 @@
           <t>NODE_S2013_14_0019</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16364,6 +16486,14 @@
         <is>
           <t>NODE_S2012_13_0050</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -16397,6 +16527,12 @@
           <t>NODE_S2013_14_0019</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16406,6 +16542,14 @@
         <is>
           <t>NODE_S2012_13_0042</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -16439,6 +16583,12 @@
           <t>NODE_S2013_14_0019</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0027</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16448,6 +16598,14 @@
         <is>
           <t>NODE_S2012_13_0043</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -16481,6 +16639,8 @@
           <t>NODE_S2013_14_0019</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16490,6 +16650,14 @@
         <is>
           <t>NODE_S2012_13_0044</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -16523,6 +16691,8 @@
           <t>NODE_S2013_14_0019</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16532,6 +16702,14 @@
         <is>
           <t>NODE_S2012_13_0047</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -16787,10 +16965,20 @@
           <t>NODE_S2013_14_0031</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -16972,10 +17160,20 @@
           <t>NODE_S2013_14_0038</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -17046,10 +17244,20 @@
           <t>NODE_S2013_14_0038</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -17157,10 +17365,24 @@
           <t>NODE_S2013_14_0043</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0046</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -17194,10 +17416,24 @@
           <t>NODE_S2013_14_0043</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0051</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -17379,10 +17615,24 @@
           <t>NODE_S2013_14_0043</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0054</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -17490,10 +17740,20 @@
           <t>NODE_S2013_14_0043</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -17601,10 +17861,24 @@
           <t>NODE_S2013_14_0043</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0046</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -17749,10 +18023,24 @@
           <t>NODE_S2013_14_0059</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0062</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -17786,10 +18074,24 @@
           <t>NODE_S2013_14_0059</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0067</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -17971,10 +18273,24 @@
           <t>NODE_S2013_14_0059</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0070</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -18082,10 +18398,20 @@
           <t>NODE_S2013_14_0059</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -18304,10 +18630,24 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0081</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -18489,10 +18829,24 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0084</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -18600,10 +18954,20 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -18711,10 +19075,24 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0081</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -18896,10 +19274,24 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0084</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -19007,10 +19399,20 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="97">
@@ -19118,10 +19520,24 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0081</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -19303,10 +19719,24 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0084</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -19414,10 +19844,20 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -19525,10 +19965,24 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0081</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -19710,10 +20164,24 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0084</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="116">
@@ -19821,10 +20289,20 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="119">
@@ -20117,10 +20595,24 @@
           <t>NODE_S2013_14_0123</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0126</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>5 týmů</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -20154,10 +20646,24 @@
           <t>NODE_S2013_14_0123</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0129</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="128">
@@ -20265,10 +20771,20 @@
           <t>NODE_S2013_14_0123</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="131">
@@ -20413,10 +20929,24 @@
           <t>NODE_S2013_14_0131</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0134</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -20450,10 +20980,24 @@
           <t>NODE_S2013_14_0131</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0137</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -20561,10 +21105,28 @@
           <t>NODE_S2013_14_0131</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0144</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0142</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="139">
@@ -20672,10 +21234,20 @@
           <t>NODE_S2013_14_0131</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="142">
@@ -20746,10 +21318,20 @@
           <t>NODE_S2013_14_0131</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="144">
@@ -20820,10 +21402,20 @@
           <t>NODE_S2013_14_0131</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -20968,10 +21560,24 @@
           <t>NODE_S2013_14_0131</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0134</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -21116,10 +21722,24 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0163</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -21153,10 +21773,20 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="155">
@@ -21227,10 +21857,28 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0160</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0153</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="157">
@@ -21338,10 +21986,20 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="160">
@@ -21412,10 +22070,20 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="162">
@@ -21523,10 +22191,28 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0155</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0171</t>
+        </is>
+      </c>
       <c r="J164" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -21708,10 +22394,28 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0160</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0153</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="170">
@@ -21819,10 +22523,28 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0176</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0174</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="173">
@@ -21930,10 +22652,20 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="176">
@@ -22004,10 +22736,20 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="178">
@@ -22078,10 +22820,20 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="180">
@@ -22152,10 +22904,20 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="182">
@@ -22374,10 +23136,24 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0187</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -22411,10 +23187,28 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0199</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0192</t>
+        </is>
+      </c>
       <c r="J188" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -22596,10 +23390,28 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0197</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0195</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="194">
@@ -22707,10 +23519,20 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="197">
@@ -22781,10 +23603,20 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="199">
@@ -22855,10 +23687,28 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0204</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0202</t>
+        </is>
+      </c>
       <c r="J200" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="201">
@@ -22966,10 +23816,20 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="204">
@@ -23040,10 +23900,20 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="206">
@@ -23188,10 +24058,24 @@
           <t>NODE_S2013_14_0206</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0210</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -23262,10 +24146,24 @@
           <t>NODE_S2013_14_0206</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0213</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="212">
@@ -23373,10 +24271,24 @@
           <t>NODE_S2013_14_0206</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0216</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="215">
@@ -23447,10 +24359,20 @@
           <t>NODE_S2013_14_0206</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="217">
@@ -23484,10 +24406,20 @@
           <t>NODE_S2013_14_0206</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="218">
@@ -23595,10 +24527,24 @@
           <t>NODE_S2013_14_0206</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0216</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="221">
@@ -23706,10 +24652,20 @@
           <t>NODE_S2013_14_0206</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="224">
@@ -23891,10 +24847,24 @@
           <t>NODE_S2013_14_0225</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0228</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -23928,10 +24898,24 @@
           <t>NODE_S2013_14_0225</t>
         </is>
       </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0233</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="230">
@@ -24113,10 +25097,24 @@
           <t>NODE_S2013_14_0225</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0236</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="235">
@@ -24224,10 +25222,20 @@
           <t>NODE_S2013_14_0225</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="238">
@@ -24335,10 +25343,24 @@
           <t>NODE_S2013_14_0225</t>
         </is>
       </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0233</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -24520,10 +25542,24 @@
           <t>NODE_S2013_14_0225</t>
         </is>
       </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0236</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="246">
@@ -24631,10 +25667,20 @@
           <t>NODE_S2013_14_0225</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="249">

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -15562,7 +15562,6 @@
           <t>NODE_S2013_14_0006</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15673,8 +15672,6 @@
           <t>NODE_S2013_14_0003</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15725,8 +15722,6 @@
           <t>NODE_S2013_14_0003</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15777,8 +15772,6 @@
           <t>NODE_S2013_14_0001</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16023,7 +16016,6 @@
           <t>NODE_S2013_14_0015</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16079,7 +16071,6 @@
           <t>NODE_S2013_14_0016</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16130,8 +16121,6 @@
           <t>NODE_S2013_14_0011</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16182,8 +16171,6 @@
           <t>NODE_S2013_14_0011</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16476,7 +16463,6 @@
           <t>NODE_S2013_14_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16532,7 +16518,6 @@
           <t>NODE_S2013_14_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16588,7 +16573,6 @@
           <t>NODE_S2013_14_0027</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16639,8 +16623,6 @@
           <t>NODE_S2013_14_0019</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16691,8 +16673,6 @@
           <t>NODE_S2013_14_0019</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16965,8 +16945,6 @@
           <t>NODE_S2013_14_0031</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17160,8 +17138,6 @@
           <t>NODE_S2013_14_0038</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17244,8 +17220,6 @@
           <t>NODE_S2013_14_0038</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17370,7 +17344,6 @@
           <t>NODE_S2013_14_0046</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17421,7 +17394,6 @@
           <t>NODE_S2013_14_0051</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17620,7 +17592,6 @@
           <t>NODE_S2013_14_0054</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17740,8 +17711,6 @@
           <t>NODE_S2013_14_0043</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17866,7 +17835,6 @@
           <t>NODE_S2013_14_0046</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18028,7 +17996,6 @@
           <t>NODE_S2013_14_0062</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18079,7 +18046,6 @@
           <t>NODE_S2013_14_0067</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18278,7 +18244,6 @@
           <t>NODE_S2013_14_0070</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18398,8 +18363,6 @@
           <t>NODE_S2013_14_0059</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18635,7 +18598,6 @@
           <t>NODE_S2013_14_0081</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18834,7 +18796,6 @@
           <t>NODE_S2013_14_0084</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18954,8 +18915,6 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19080,7 +19039,6 @@
           <t>NODE_S2013_14_0081</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19279,7 +19237,6 @@
           <t>NODE_S2013_14_0084</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19399,8 +19356,6 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19525,7 +19480,6 @@
           <t>NODE_S2013_14_0081</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19724,7 +19678,6 @@
           <t>NODE_S2013_14_0084</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19844,8 +19797,6 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19970,7 +19921,6 @@
           <t>NODE_S2013_14_0081</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20169,7 +20119,6 @@
           <t>NODE_S2013_14_0084</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20289,8 +20238,6 @@
           <t>NODE_S2013_14_0072</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20600,7 +20547,6 @@
           <t>NODE_S2013_14_0126</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20651,7 +20597,6 @@
           <t>NODE_S2013_14_0129</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20771,8 +20716,6 @@
           <t>NODE_S2013_14_0123</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20934,7 +20877,6 @@
           <t>NODE_S2013_14_0134</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20985,7 +20927,6 @@
           <t>NODE_S2013_14_0137</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21234,8 +21175,6 @@
           <t>NODE_S2013_14_0131</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21318,8 +21257,6 @@
           <t>NODE_S2013_14_0131</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21402,8 +21339,6 @@
           <t>NODE_S2013_14_0131</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21565,7 +21500,6 @@
           <t>NODE_S2013_14_0134</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21727,7 +21661,6 @@
           <t>NODE_S2013_14_0163</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21773,8 +21706,6 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21986,8 +21917,6 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22070,8 +21999,6 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22652,8 +22579,6 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22736,8 +22661,6 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22820,8 +22743,6 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22904,8 +22825,6 @@
           <t>NODE_S2013_14_0150</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23141,7 +23060,6 @@
           <t>NODE_S2013_14_0187</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23519,8 +23437,6 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23603,8 +23519,6 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23816,8 +23730,6 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23900,8 +23812,6 @@
           <t>NODE_S2013_14_0182</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24063,7 +23973,6 @@
           <t>NODE_S2013_14_0210</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24151,7 +24060,6 @@
           <t>NODE_S2013_14_0213</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24276,7 +24184,6 @@
           <t>NODE_S2013_14_0216</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24359,8 +24266,6 @@
           <t>NODE_S2013_14_0206</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24406,8 +24311,6 @@
           <t>NODE_S2013_14_0206</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24532,7 +24435,6 @@
           <t>NODE_S2013_14_0216</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24652,8 +24554,6 @@
           <t>NODE_S2013_14_0206</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24852,7 +24752,6 @@
           <t>NODE_S2013_14_0228</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24903,7 +24802,6 @@
           <t>NODE_S2013_14_0233</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>complete</t>
@@ -25102,7 +25000,6 @@
           <t>NODE_S2013_14_0236</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>complete</t>
@@ -25222,8 +25119,6 @@
           <t>NODE_S2013_14_0225</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>complete</t>
@@ -25348,7 +25243,6 @@
           <t>NODE_S2013_14_0233</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>complete</t>
@@ -25547,7 +25441,6 @@
           <t>NODE_S2013_14_0236</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>complete</t>
@@ -25667,8 +25560,6 @@
           <t>NODE_S2013_14_0225</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>complete</t>
@@ -45069,7 +44960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45165,6 +45056,18 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PSG Zlín</t>
         </is>
       </c>
     </row>

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -15131,7 +15131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15180,6 +15180,23 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0031</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -45126,9 +45143,22 @@
       </c>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>(žádné otevřené položky — sezóna OK)</t>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0031</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
         </is>
       </c>
     </row>

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -9455,7 +9455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W34"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11327,6 +11327,995 @@
       <c r="U34" s="2" t="n"/>
       <c r="V34" s="2" t="n"/>
       <c r="W34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0251</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RH-Centrum Brno</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0251</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0287</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00287</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0251</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0288</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00288</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0251</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0289</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HLC Bulldogs Brno</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0251</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0290</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00290</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TJ Šenkovice</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0251</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0291</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TJ Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0292</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>HC Lukáš</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0293</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00293</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0294</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00294</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0295</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Krhov</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0296</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HKD Drakstav</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0297</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>7</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Veselý Team</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0298</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0299</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0300</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00300</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0301</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0302</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0303</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HC STST Chvojkovice-Brod</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0304</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00304</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0305</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0306</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>9</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0307</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00307</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15269,7 +16258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N249"/>
+  <dimension ref="A1:N253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25625,6 +26614,154 @@
       <c r="J249" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0249</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>REG_PHA</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0038</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Karlovarský – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>REG_KVK</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0120</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0182</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Vysočina – Třebíč</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0182</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -31477,7 +32614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J284"/>
+  <dimension ref="A1:J308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -44963,6 +46100,654 @@
       <c r="J284" t="inlineStr">
         <is>
           <t>Orlová</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Slovan Louny</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Slovan Louny</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>HC Cheb 2001</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>HC Cheb 2001</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>30KVRY</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>RH-Centrum Brno</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>RH-Centrum Brno</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>HLC Bulldogs Brno</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>HLC Bulldogs Brno</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>TJ Šenkovice</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>TJ Šenkovice</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>TJ Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>TJ Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>HC Lukáš</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>HC Lukáš</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0294</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Krhov</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Krhov</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>HKD Drakstav</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>HKD Drakstav</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Veselý Team</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Veselý Team</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0304</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>HC STST Chvojkovice-Brod</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>HC STST Chvojkovice-Brod</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
     </row>
@@ -49828,7 +51613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -51694,6 +53479,118 @@
       <c r="V25" t="inlineStr">
         <is>
           <t>TR_S2013_14_00104</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0249</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0249</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0284</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00284</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Slovan Louny</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0249</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0285</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00285</t>
         </is>
       </c>
     </row>
@@ -62123,7 +64020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -63208,6 +65105,73 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0250</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HC Cheb 2001</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0250</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S2013_14_0286</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S2013_14_00286</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +86,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -95,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +115,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -46884,7 +46895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -46941,11 +46952,89 @@
           <t>NODE_S2013_14_0031</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>skupina A (celostátní) · NODE_S2013_14_0033</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC BAK Trutnov (HK), HC Hvězda Praha (PRA)), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor (Praha) · NODE_S2013_14_0249</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Roudnice nad Labem, Slovan Louny), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Karlovarský – Krajská liga (Karlovarský kraj) · NODE_S2013_14_0250</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC Cheb 2001), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,6 +117,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -16131,7 +16134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16195,6 +16198,57 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0033</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC BAK Trutnov (HK), HC Hvězda Praha (PRA)), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0249</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Roudnice nad Labem, Slovan Louny), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0250</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC Cheb 2001), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -46972,7 +47026,7 @@
           <t>skupina A (celostátní) · NODE_S2013_14_0033</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC BAK Trutnov (HK), HC Hvězda Praha (PRA)), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -46998,7 +47052,7 @@
           <t>Praha – Pražský přebor (Praha) · NODE_S2013_14_0249</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Roudnice nad Labem, Slovan Louny), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -47024,7 +47078,7 @@
           <t>Karlovarský – Krajská liga (Karlovarský kraj) · NODE_S2013_14_0250</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC Cheb 2001), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -18112,7 +18112,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -18313,7 +18313,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SK Černošice – HC Rakovník   7:1,2:5,1:3</t>
+          <t>SK Černošice – HC Rakovník 7:1,2:5,1:3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Spartak Vlašim – HC Jesenice  1:2 SN,3:6</t>
+          <t>Spartak Vlašim – HC Jesenice 1:2 SN,3:6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BK Mladá Boleslav "B" – HC Junior Mělník  1:10,4:5 SN</t>
+          <t>BK Mladá Boleslav "B" – HC Junior Mělník 1:10,4:5 SN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Slavoj Velké Popovice – HC Příbram  5:4 SN,2:7,2:1</t>
+          <t>Slavoj Velké Popovice – HC Příbram 5:4 SN,2:7,2:1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Slavoj Velké Popovice – HC Rakovník   4:2,1:2,1:2</t>
+          <t>Slavoj Velké Popovice – HC Rakovník 4:2,1:2,1:2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HC Junior Mělník – HC Jesenice  5:4,3:4,3:2</t>
+          <t>HC Junior Mělník – HC Jesenice 5:4,3:4,3:2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HC Junior Mělník – HC Rakovník  6:4,1:4,0:1</t>
+          <t>HC Junior Mělník – HC Rakovník 6:4,1:4,0:1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IHC Písek – Jiskra Humpolec  4:3,2:0</t>
+          <t>IHC Písek – Jiskra Humpolec 4:3,2:0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>David servis České Budějovice  - HC Vimperk 10:3,6:3</t>
+          <t>David servis České Budějovice - HC Vimperk 10:3,6:3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -19213,7 +19213,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lokomotiva Veselí nad Lužnicí  - OLH Spartak Soběslav 5:2,7:5</t>
+          <t>Lokomotiva Veselí nad Lužnicí - OLH Spartak Soběslav 5:2,7:5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Slavoj Český Krumlov – HC Strakonice  2:1,4:11,3:6</t>
+          <t>Slavoj Český Krumlov – HC Strakonice 2:1,4:11,3:6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IHC Písek – HC Strakonice  3:6,3:5</t>
+          <t>IHC Písek – HC Strakonice 3:6,3:5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>David servis České Budějovice  - Lokomotiva Veselí nad Lužnicí 5:2,5:4</t>
+          <t>David servis České Budějovice - Lokomotiva Veselí nad Lužnicí 5:2,5:4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>David servis České Budějovice – HC Strakonice  5:2,4:2</t>
+          <t>David servis České Budějovice – HC Strakonice 5:2,4:2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SKP Rapid Plzeň  - TJ Město Zbiroh "A" 3:5, 0:5 K</t>
+          <t>SKP Rapid Plzeň - TJ Město Zbiroh "A" 3:5, 0:5 K</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Jiskra Bezdružice – 1.LHC Kralovice 1991  0:2, 3:5</t>
+          <t>Jiskra Bezdružice – 1.LHC Kralovice 1991 0:2, 3:5</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -21516,7 +21516,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -21809,7 +21809,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HC Česká Lípa – HC Lomnice nad Popelkou  5:3,8:2</t>
+          <t>HC Česká Lípa – HC Lomnice nad Popelkou 5:3,8:2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HC Jičín – TJ BK Nová Paka   11:6,2:4,4:5</t>
+          <t>HC Jičín – TJ BK Nová Paka 11:6,2:4,4:5</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Spartak Nové Město nad Metují  - Wikow Hronov 4:3,0:1,3:2 SN</t>
+          <t>Spartak Nové Město nad Metují - Wikow Hronov 4:3,0:1,3:2 SN</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HC Náchod – TJ BK Nová Paka  7:0,2:3 SN,7:0</t>
+          <t>HC Náchod – TJ BK Nová Paka 7:0,2:3 SN,7:0</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -22186,7 +22186,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HC Trutnov – Spartak Nové Město nad Metují  2:1,6:1</t>
+          <t>HC Trutnov – Spartak Nové Město nad Metují 2:1,6:1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -22350,7 +22350,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Spartak Nové Město nad Metují  - TJ BK Nová Paka 6:4,7:1</t>
+          <t>Spartak Nové Město nad Metují - TJ BK Nová Paka 6:4,7:1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HC Náchod – HC Trutnov  1:4,0:2</t>
+          <t>HC Náchod – HC Trutnov 1:4,0:2</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -22891,7 +22891,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Spartak Polička – HC Skuteč  4:3 PP,2:1</t>
+          <t>Spartak Polička – HC Skuteč 4:3 PP,2:1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -22928,7 +22928,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HC Hlinsko – Orli Lanškroun  8:2,10:2</t>
+          <t>HC Hlinsko – Orli Lanškroun 8:2,10:2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Spartak Polička – HC Hlinsko  6:1,2:6,3:4</t>
+          <t>Spartak Polička – HC Hlinsko 6:1,2:6,3:4</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -23221,7 +23221,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Spartak Choceň – HC Litomyšl  3:4,1:3,4:1,5:3,1:2</t>
+          <t>Spartak Choceň – HC Litomyšl 3:4,1:3,4:1,5:3,1:2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -23258,7 +23258,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou  - Kohouti Česká Třebová  19:1,6:4,7:3</t>
+          <t>HC Světlá nad Sázavou - Kohouti Česká Třebová 19:1,6:4,7:3</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou  - HC Litomyšl   1:2,7:1,8:5,4:1</t>
+          <t>HC Světlá nad Sázavou - HC Litomyšl 1:2,7:1,8:5,4:1</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová – HC Chotěboř  7:1,1:2 PP,8:2,3:4,1:2 SN</t>
+          <t>Slovan Moravská Třebová – HC Chotěboř 7:1,1:2 PP,8:2,3:4,1:2 SN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -23918,7 +23918,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou  - HC Chotěboř 3:1,7:1,4:3 SN</t>
+          <t>HC Světlá nad Sázavou - HC Chotěboř 3:1,7:1,4:3 SN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -23955,7 +23955,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Sokol Křižanov – TJ Náměšť nad Oslavou  5:7, 2:7</t>
+          <t>Sokol Křižanov – TJ Náměšť nad Oslavou 5:7, 2:7</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Spartak Velká Bíteš "B" - RH-Centrum  Brno 1:8, 5:3, nájezdy 0:1</t>
+          <t>Spartak Velká Bíteš "B" - RH-Centrum Brno 1:8, 5:3, nájezdy 0:1</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HC Zastávka – Sokol Křižanov  (po dohodě nehráno)</t>
+          <t>HC Zastávka – Sokol Křižanov (po dohodě nehráno)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RH-Centrum Brno  - SK Telč 6:3, 9:2</t>
+          <t>RH-Centrum Brno - SK Telč 6:3, 9:2</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RH-Centrum Brno – TJ Náměšť nad Oslavou 15:4, 0:1,  nájezdy 1:0</t>
+          <t>RH-Centrum Brno – TJ Náměšť nad Oslavou 15:4, 0:1, nájezdy 1:0</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -24942,7 +24942,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -25153,7 +25153,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>TJ Šternberk – HCM Warrior Brno  1:3,1:3</t>
+          <t>TJ Šternberk – HCM Warrior Brno 1:3,1:3</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -25190,7 +25190,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SK Minerva Boskovice – Dynamiters Blansko  2:3 SN,4:1,1:4</t>
+          <t>SK Minerva Boskovice – Dynamiters Blansko 2:3 SN,4:1,1:4</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -25277,7 +25277,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – HCM Warrior Brno  8:3,3:1</t>
+          <t>HHK Velké Meziříčí – HCM Warrior Brno 8:3,3:1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – HC Spartak Velká Bíteš  4:5 PP,2:4,3:2 SN,4:6</t>
+          <t>HHK Velké Meziříčí – HC Spartak Velká Bíteš 4:5 PP,2:4,3:2 SN,4:6</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HC Brumov-Bylnice – HC Uherské Hradiště  7:3,7:1,8:4</t>
+          <t>HC Brumov-Bylnice – HC Uherské Hradiště 7:3,7:1,8:4</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HC Uherský Brod – Hokej Uherský Ostroh  8:4,6:2,5:3</t>
+          <t>HC Uherský Brod – Hokej Uherský Ostroh 8:4,6:2,5:3</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HC Brumov-Bylnice  - HC Uherský Brod 6:3,4:5 SN,5:4,3:2</t>
+          <t>HC Brumov-Bylnice - HC Uherský Brod 6:3,4:5 SN,5:4,3:2</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -25721,7 +25721,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -25895,7 +25895,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SK Karviná – HC Rožnov pod Radhoštěm  "A"  8:3,12:3</t>
+          <t>SK Karviná – HC Rožnov pod Radhoštěm "A" 8:3,12:3</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -25932,7 +25932,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>HK Hokej Šumperk 2003  - HC Rožnov pod Radhoštěm "B"  14:0,0:2,6:2</t>
+          <t>HK Hokej Šumperk 2003 - HC Rožnov pod Radhoštěm "B" 14:0,0:2,6:2</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HC Studénka – HK Krnov  0:5 K,2:7</t>
+          <t>HC Studénka – HK Krnov 0:5 K,2:7</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>TJ Horní Benešov – HC Kopřivnice  5:0 K,0:8,4:1</t>
+          <t>TJ Horní Benešov – HC Kopřivnice 5:0 K,0:8,4:1</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -26093,7 +26093,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SK Karviná – HK Krnov  6:4,5:1</t>
+          <t>SK Karviná – HK Krnov 6:4,5:1</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HK Hokej Šumperk 2003 – TJ Horní Benešov  5:4,5:1</t>
+          <t>HK Hokej Šumperk 2003 – TJ Horní Benešov 5:4,5:1</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -26212,7 +26212,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>SK Karviná – HK Hokej Šumperk 2003  6:3,3:2 PP</t>
+          <t>SK Karviná – HK Hokej Šumperk 2003 6:3,3:2 PP</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HK Hokej Šumperk 2003  - HC Bohumín  5:6 PP,3:5</t>
+          <t>HK Hokej Šumperk 2003 - HC Bohumín 5:6 PP,3:5</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -26373,7 +26373,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HC Studénka – HC Rožnov pod Radhoštěm "A"  8:0,3:4,7:2</t>
+          <t>HC Studénka – HC Rožnov pod Radhoštěm "A" 8:0,3:4,7:2</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>HC Kopřivnice – HK Krnov  10:3,4:3</t>
+          <t>HC Kopřivnice – HK Krnov 10:3,4:3</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>HC Studénka – HC Bohumín  6:4,13:5</t>
+          <t>HC Studénka – HC Bohumín 6:4,13:5</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -26571,7 +26571,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>HC Kopřivnice – HC Rožnov pod Radhoštěm "B"  3:2 SN,3:4 PP,8:2</t>
+          <t>HC Kopřivnice – HC Rožnov pod Radhoštěm "B" 3:2 SN,3:4 PP,8:2</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -26653,7 +26653,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HC Studénka – HC Kopřivnice  1:3,1:4</t>
+          <t>HC Studénka – HC Kopřivnice 1:3,1:4</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">

--- a/data/S2013_14_FINAL.xlsx
+++ b/data/S2013_14_FINAL.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -30423,7 +30423,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -30501,7 +30501,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -30579,7 +30579,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -30657,7 +30657,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -30818,7 +30818,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -30896,7 +30896,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -30974,7 +30974,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -31052,7 +31052,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -31130,7 +31130,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -31208,7 +31208,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -31286,7 +31286,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -31442,7 +31442,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -54044,7 +54044,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -54122,7 +54122,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -54200,7 +54200,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -54278,7 +54278,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -54356,7 +54356,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -54434,7 +54434,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -54512,7 +54512,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -54595,7 +54595,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -54673,7 +54673,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -54751,7 +54751,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -54829,7 +54829,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -54907,7 +54907,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
